--- a/recipes/onion-garlic-free-indian/focus-states/03-odisha/excel/odisha-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/03-odisha/excel/odisha-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Santula</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Santula</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Side  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -1728,36 +1731,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Boil, drain, temper, toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Boil, drain, temper, toss. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 124  ·  Protein 4 g  ·  Carbs 19 g  ·  Fat 4 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Santula: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1771,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1783,7 +1952,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Besara Mixed Veg</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Besara Mixed Veg</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1793,7 +1962,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Side  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1813,44 +1982,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2034,36 +2203,215 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Temper panch phoron. Add veg and mustard paste. Cook until the oil shines.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Temper panch phoron. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Add veg and mustard paste. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Cook until the oil shines. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 184  ·  Protein 4 g  ·  Carbs 18 g  ·  Fat 11 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Besara Mixed Veg: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2077,7 +2425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2089,7 +2437,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Saga Bhaja</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Saga Bhaja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2099,7 +2447,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Side  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2119,44 +2467,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2304,34 +2652,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Temper, wilt greens. No onion, no garlic.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Temper, wilt greens. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>No onion, no garlic. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 152  ·  Protein 3 g  ·  Carbs 14 g  ·  Fat 10 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Saga Bhaja: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2345,7 +2859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2357,7 +2871,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Luchi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Luchi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2367,7 +2881,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Bread  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2387,44 +2901,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2572,34 +3086,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry small puffed breads in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry small puffed breads in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 352  ·  Protein 6 g  ·  Carbs 48 g  ·  Fat 15 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Luchi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2613,7 +3280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2625,7 +3292,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pakhala Rice</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pakhala Rice</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2635,7 +3302,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Bread  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2655,44 +3322,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -2876,36 +3543,215 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="54" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Soak rice in water (or whey). Season. Serve with saga and badi.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Soak rice in water (or whey). Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Season. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Serve with saga and badi. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 378  ·  Protein 8 g  ·  Carbs 81 g  ·  Fat 1 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Pakhala Rice: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2919,7 +3765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2931,7 +3777,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Poda Pitha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Poda Pitha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2941,7 +3787,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Bread  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2961,44 +3807,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 20 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3182,36 +4028,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Mix, bake in a greased steel pot on low until the crust is charred-caramel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or earthen pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Mix, bake in a greased steel pot on low until the crust is charred-caramel. Work in Steel or earthen pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 342  ·  Protein 3 g  ·  Carbs 49 g  ·  Fat 15 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Poda Pitha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3225,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3237,7 +4236,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chhena Poda</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chhena Poda</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3247,7 +4246,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Sweet  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3267,44 +4266,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>Prep 20 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -3470,35 +4469,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Bake until the top is burnt caramel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel baking dish — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Bake until the top is burnt caramel. Work in Steel baking dish — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 334  ·  Protein 11 g  ·  Carbs 34 g  ·  Fat 19 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Chhena Poda: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3512,7 +4664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3524,7 +4676,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chhena Jhili</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chhena Jhili</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3534,7 +4686,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Sweet  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3554,44 +4706,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -3739,34 +4891,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry balls in ghee, soak in warm syrup made in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry balls in ghee, soak in warm syrup made in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 416  ·  Protein 11 g  ·  Carbs 71 g  ·  Fat 12 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Chhena Jhili: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3780,7 +5085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3792,7 +5097,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gaja</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gaja</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3802,7 +5107,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Sweet  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3822,44 +5127,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3989,33 +5294,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cut diamonds, fry, soak briefly in syrup.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cut diamonds, fry, soak briefly in syrup. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 532  ·  Protein 6 g  ·  Carbs 110 g  ·  Fat 8 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Gaja: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4029,7 +5487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4041,7 +5499,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rasabali</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rasabali</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4051,7 +5509,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Dessert  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4071,44 +5529,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -4256,34 +5714,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Sear patties, soak in thickened steel-pot milk.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Sear patties, soak in thickened steel-pot milk. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 306  ·  Protein 13 g  ·  Carbs 33 g  ·  Fat 15 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Rasabali: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4561,7 +6172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4573,7 +6184,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kheeri</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kheeri</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4583,7 +6194,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Dessert  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4603,44 +6214,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 10 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -4824,36 +6435,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel until creamy.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel until creamy. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 444  ·  Protein 12 g  ·  Carbs 78 g  ·  Fat 10 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Kheeri: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4867,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4879,7 +6643,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Manda Pitha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Manda Pitha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4889,7 +6653,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Dessert  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4909,44 +6673,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 30 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -5058,32 +6822,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Fill, steam 12 minutes in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Fill, steam 12 minutes in steel. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 357  ·  Protein 5 g  ·  Carbs 47 g  ·  Fat 17 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Manda Pitha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5097,7 +7014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5109,7 +7026,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Amba Khatta</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Amba Khatta</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5119,7 +7036,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Salad  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5139,44 +7056,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Prep 10 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -5378,37 +7295,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper, cook 5 minutes until glossy.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Temper, cook 5 minutes until glossy. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 129  ·  Protein 1 g  ·  Carbs 33 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Amba Khatta: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5422,7 +7505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5434,7 +7517,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Khatta</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Khatta</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5444,7 +7527,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Salad  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5464,44 +7547,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Prep 10 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -5667,35 +7750,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook to a relish.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook to a relish. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 107  ·  Protein 1 g  ·  Carbs 27 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Khatta: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5709,7 +7945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5721,7 +7957,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cucumber Lemon Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cucumber Lemon Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5731,7 +7967,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Salad  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5751,44 +7987,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5954,35 +8190,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 20  ·  Protein 1 g  ·  Carbs 5 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Cucumber Lemon Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9032,7 +11434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9044,7 +11446,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Chakuli Pitha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Chakuli Pitha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9054,7 +11456,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Starter  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9074,44 +11476,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9259,34 +11661,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Grind, spread on iron tawa, cook both sides.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Grind, spread on iron tawa, cook both sides. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 285  ·  Protein 7 g  ·  Carbs 47 g  ·  Fat 8 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Chakuli Pitha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9300,7 +11855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9312,7 +11867,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Enduri Pitha</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Enduri Pitha</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9322,7 +11877,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Starter  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9342,44 +11897,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 30 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -9509,33 +12064,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Spread batter on leaf, fill, fold, steam in steel 15 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Spread batter on leaf, fill, fold, steam in steel 15 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 313  ·  Protein 5 g  ·  Carbs 45 g  ·  Fat 13 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Enduri Pitha: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9549,7 +12257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9561,7 +12269,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bara (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bara (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9571,7 +12279,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Starter  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9591,44 +12299,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9830,37 +12538,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Grind fluffy, fry rings in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Grind fluffy, fry rings in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 196  ·  Protein 10 g  ·  Carbs 23 g  ·  Fat 8 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Bara (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9874,7 +12748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9886,7 +12760,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dalma</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dalma</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9896,7 +12770,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Main  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9916,44 +12790,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 15 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -10173,38 +13047,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Cook dal and veg together. Cumin-ginger-ghee tadka. Never aluminium, never allium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Cook dal and veg together. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Cumin-ginger-ghee tadka. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Never aluminium, never allium. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 310  ·  Protein 10 g  ·  Carbs 54 g  ·  Fat 8 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Dalma: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10218,7 +13271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10230,7 +13283,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Temple Khichdi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Temple Khichdi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10240,7 +13293,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Main  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10260,44 +13313,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10499,37 +13552,229 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook together very soft. Ghee tadka. This is mahaprasad style.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel or clay pot — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook together very soft. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Ghee tadka. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>This is mahaprasad style. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 219  ·  Protein 6 g  ·  Carbs 32 g  ·  Fat 7 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Temple Khichdi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="33">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10543,7 +13788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10555,7 +13800,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kanika</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kanika</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10565,7 +13810,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Odisha kitchen  ·  Main  ·  Odia temple and home kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Odisha  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10585,44 +13830,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -10824,37 +14069,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Fry spices and nuts in ghee. Cook rice. Slightly sweet, no onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Fry spices and nuts in ghee. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Cook rice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Slightly sweet, no onion. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 142  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 11 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Kanika: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
